--- a/ecosysem/db/Excels/DeltaG0f.xlsx
+++ b/ecosysem/db/Excels/DeltaG0f.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emartinez\Documents\GitHub\EcoSysEM\ecosysem\db\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F991E152-3A58-4A97-9ED8-35F46CF01067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{55B87AD8-A28D-4D56-8131-E9616800B4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3795" yWindow="-20475" windowWidth="28800" windowHeight="15345" xr2:uid="{A62AFDAB-FBC8-40CE-9878-3FD750A8957F}"/>
+    <workbookView xWindow="28695" yWindow="-3330" windowWidth="19410" windowHeight="20985" xr2:uid="{A62AFDAB-FBC8-40CE-9878-3FD750A8957F}"/>
   </bookViews>
   <sheets>
-    <sheet name="DeltaG" sheetId="1" r:id="rId1"/>
+    <sheet name="DeltaG0f" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="116">
   <si>
     <t>IUPAC</t>
   </si>
@@ -339,12 +339,87 @@
   </si>
   <si>
     <t>CH1.8O0.5N0.2</t>
+  </si>
+  <si>
+    <t>Methanol</t>
+  </si>
+  <si>
+    <t>Lactate</t>
+  </si>
+  <si>
+    <t>CH3OH</t>
+  </si>
+  <si>
+    <t>CH3CHOHCOO-</t>
+  </si>
+  <si>
+    <t>Ethanol</t>
+  </si>
+  <si>
+    <t>CH3CH2OH</t>
+  </si>
+  <si>
+    <t>Propionic acid</t>
+  </si>
+  <si>
+    <t>Propionate</t>
+  </si>
+  <si>
+    <t>CH3CH2CO2H</t>
+  </si>
+  <si>
+    <t>CH3CH2CO2-</t>
+  </si>
+  <si>
+    <t>Glycerol</t>
+  </si>
+  <si>
+    <t>C3H5(OH)3</t>
+  </si>
+  <si>
+    <t>Acetone</t>
+  </si>
+  <si>
+    <t>CH3COCH3</t>
+  </si>
+  <si>
+    <t>Butyrate</t>
+  </si>
+  <si>
+    <t>CH3CH2CH2COOH</t>
+  </si>
+  <si>
+    <t>CH3CH2CH2COO-</t>
+  </si>
+  <si>
+    <t>Butanol</t>
+  </si>
+  <si>
+    <t>CH3CH2CH2CH2OH</t>
+  </si>
+  <si>
+    <t>Benzoate</t>
+  </si>
+  <si>
+    <t>C6H5COO-</t>
+  </si>
+  <si>
+    <t>Butanoic acid</t>
+  </si>
+  <si>
+    <t>Propanol</t>
+  </si>
+  <si>
+    <t>CH3(CH2)2OH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -382,13 +457,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -742,14 +823,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC731D4-E3C1-4B64-BF1D-C3C9432561A9}">
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.28515625" style="3" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.28515625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1670,6 +1751,211 @@
         <v>23</v>
       </c>
     </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>92</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D55" s="3">
+        <v>-175.4</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>93</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D56" s="3">
+        <v>-517.1</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>96</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" s="3">
+        <v>-181.8</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>98</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D58" s="4">
+        <v>-391</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>99</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D59" s="3">
+        <v>-361.1</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>102</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D60" s="3">
+        <v>-488.5</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>104</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D61" s="3">
+        <v>-159.80000000000001</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>114</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D62" s="3">
+        <v>-175.36</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>113</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D63" s="5">
+        <v>-381.63</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>106</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D64" s="3">
+        <v>-352.6</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>109</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D65" s="4">
+        <v>-162.51</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>111</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D66" s="4">
+        <f>-385.2-298.15*0.1676</f>
+        <v>-435.16994</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
